--- a/Dados-apoio/proj-2015-2019-POP-60+RIPSA.xlsx
+++ b/Dados-apoio/proj-2015-2019-POP-60+RIPSA.xlsx
@@ -31,1939 +31,1939 @@
     <t xml:space="preserve">POP60</t>
   </si>
   <si>
-    <t xml:space="preserve"> ADAMANTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ADOLFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUAS DA PRATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUAS DE LINDOIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUAS DE SANTA BARBARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUAS DE SAO PEDRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUDOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALAMBARI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALFREDO MARCONDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALTAIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALTINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALTO ALEGRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALUMINIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALVARES FLORENCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALVARES MACHADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALVARO DE CARVALHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALVINLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMERICANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMERICO BRASILIENSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMERICO DE CAMPOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMPARO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ANALANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ANDRADINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ANGATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ANHEMBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ANHUMAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> APARECIDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> APARECIDA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> APIAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARACARIGUAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARACATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARACOIABA DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARAMINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARANDU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARAPEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARARAQUARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARARAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARCO-IRIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AREALVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AREIAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AREIOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARIRANHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARTUR NOGUEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARUJA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ASPASIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ASSIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ATIBAIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AURIFLAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AVAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AVANHANDAVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AVARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BADY BASSITT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BALBINOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BALSAMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BANANAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARAO DE ANTONINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARBOSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARIRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARRA BONITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARRA DO CHAPEU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARRA DO TURVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARRETOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARRINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARUERI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BASTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BATATAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BAURU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BEBEDOURO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BENTO DE ABREU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BERNARDINO DE CAMPOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BERTIOGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BILAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BIRIGUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BIRITIBA MIRIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOA ESPERANCA DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOCAINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOFETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOITUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOM JESUS DOS PERDOES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOM SUCESSO DE ITARARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BORACEIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BORBOREMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOREBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOTUCATU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BRAGANCA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BRAUNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BREJO ALEGRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BRODOWSKI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BROTAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BURI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BURITAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BURITIZAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CABRALIA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CABREUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CACAPAVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CACHOEIRA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CACONDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAFELANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAIABU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAIEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAIUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAJAMAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAJATI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAJOBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAJURU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAMPINA DO MONTE ALEGRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAMPINAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAMPO LIMPO PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAMPOS DO JORDAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAMPOS NOVOS PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CANANEIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CANAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CANDIDO MOTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CANDIDO RODRIGUES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CANITAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAPAO BONITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAPELA DO ALTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAPIVARI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CARAGUATATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CARAPICUIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CARDOSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CASA BRANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CASSIA DOS COQUEIROS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CASTILHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CATANDUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CATIGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CEDRAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CERQUEIRA CESAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CERQUILHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CESARIO LANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CHARQUEADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CLEMENTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COLINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COLOMBIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CONCHAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CONCHAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CORDEIROPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COROADOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CORONEL MACEDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CORUMBATAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COSMOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COSMORAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COTIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CRAVINHOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CRISTAIS PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CRUZALIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CRUZEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CUBATAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CUNHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DESCALVADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DIADEMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DIRCE REIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DIVINOLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DOBRADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DOIS CORREGOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DOLCINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DOURADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DRACENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DUARTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DUMONT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ECHAPORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ELDORADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ELIAS FAUSTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ELISIARIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EMBAUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EMBU DAS ARTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EMBU-GUACU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EMILIANOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ENGENHEIRO COELHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESPIRITO SANTO DO PINHAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESPIRITO SANTO DO TURVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESTRELA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESTRELA DO NORTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EUCLIDES DA CUNHA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FARTURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FERNANDOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FERNANDO PRESTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FERNAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FERRAZ DE VASCONCELOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FLORA RICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FLOREAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FLORIDA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FLORINEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FRANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FRANCISCO MORATO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FRANCO DA ROCHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GABRIEL MONTEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GALIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GARCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GASTAO VIDIGAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GAVIAO PEIXOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GENERAL SALGADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GETULINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GLICERIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAICARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAIMBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAPIACU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAPIARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARACAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARACI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARANI D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARANTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARARAPES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARAREMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARATINGUETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAREI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARUJA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARULHOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUATAPARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUZOLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HERCULANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HOLAMBRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HORTOLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IACANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IACRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IARAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IBATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IBIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IBIRAREMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IBITINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IBIUNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ICEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IEPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IGARACU DO TIETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IGARAPAVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IGARATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IGUAPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ILHABELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ILHA COMPRIDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ILHA SOLTEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INDAIATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INDIANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INDIAPORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INUBIA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPAUSSU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPERO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPEUNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPIGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPORANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IRACEMAPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IRAPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IRAPURU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITABERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAJOBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAJU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITANHAEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAOCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPECERICA DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPETININGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPEVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPEVI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPIRAPUA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPORANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAQUAQUECETUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITARARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITARIRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITATIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITATINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITIRAPINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITIRAPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITOBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITUPEVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITUVERAVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JABORANDI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JABOTICABAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JACAREI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JACI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JACUPIRANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JAGUARIUNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JAMBEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JANDIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JARDINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JARINU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JAU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JERIQUARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JOANOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JOAO RAMALHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JOSE BONIFACIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JULIO MESQUITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JUMIRIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JUNDIAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JUNQUEIROPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JUQUIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JUQUITIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LAGOINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LARANJAL PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LAVINIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LAVRINHAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LEME</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LENCOIS PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LIMEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LINDOIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LINS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LORENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LOURDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LOUVEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUCELIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUCIANOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUIS ANTONIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUIZIANIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUPERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUTECIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MACATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MACAUBAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MACEDONIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MAGDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MAIRINQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MAIRIPORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MANDURI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARABA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARACAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARAPOAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARIAPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARILIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARTINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MATAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MAUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MENDONCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MERIDIANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MESOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIGUELOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MINEIROS DO TIETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRACATU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRA ESTRELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRANDOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRANTE DO PARANAPANEMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRASSOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRASSOLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOCOCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOGI DAS CRUZES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOGI GUACU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOGI MIRIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOMBUCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONCOES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONGAGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE ALEGRE DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE ALTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE APRAZIVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE AZUL PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE CASTELO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTEIRO LOBATO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE MOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MORRO AGUDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MORUNGABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOTUCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MURUTINGA DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NANTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NARANDIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NATIVIDADE DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NAZARE PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NEVES PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NHANDEARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NIPOA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA ALIANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA CAMPINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA CANAA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA CASTILHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA EUROPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA GRANADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA GUATAPORANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA LUZITANIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA ODESSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVO HORIZONTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NUPORANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OCAUCU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OLEO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OLIMPIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ONDA VERDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ORIENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ORINDIUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ORLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OSASCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OSCAR BRESSANE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OSVALDO CRUZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OURINHOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OUROESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OURO VERDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PACAEMBU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PALESTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PALMARES PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PALMEIRA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PALMITAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PANORAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARAGUACU PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARAIBUNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARAISO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARANAPANEMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARANAPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARAPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARDINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARIQUERA-ACU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARISI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PATROCINIO PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PAULICEIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PAULINIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PAULISTANIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PAULO DE FARIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDERNEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDRA BELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDRANOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDREGULHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDREIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDRINHAS PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDRO DE TOLEDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PENAPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEREIRA BARRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEREIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PERUIBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIACATU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIEDADE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PILAR DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PINDAMONHANGABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PINDORAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PINHALZINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIQUEROBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIQUETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRACAIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRACICABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRAJU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRAJUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRANGI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRAPORA DO BOM JESUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRAPOZINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRASSUNUNGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRATININGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PITANGUEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PLANALTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PLATINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POLONI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POMPEIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PONGAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PONTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PONTALINDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PONTES GESTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POPULINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PORANGABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PORTO FELIZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PORTO FERREIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POTIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POTIRENDABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRACINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRADOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRAIA GRANDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRATANIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRESIDENTE ALVES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRESIDENTE BERNARDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRESIDENTE EPITACIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRESIDENTE PRUDENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRESIDENTE VENCESLAU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PROMISSAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> QUADRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> QUATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> QUEIROZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> QUELUZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> QUINTANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RAFARD</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RANCHARIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> REDENCAO DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> REGENTE FEIJO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> REGINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> REGISTRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RESTINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO BONITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO CORRENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO DOS INDIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO GRANDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO PIRES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO PRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIVERSUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIFAINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RINCAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIO CLARO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIO DAS PEDRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIO GRANDE DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIOLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ROSANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ROSEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RUBIACEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RUBINEIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SABINO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAGRES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALES OLIVEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALESOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALMOURAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALTINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALTO DE PIRAPORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALTO GRANDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANDOVALINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA ADELIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA ALBERTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA BARBARA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA BRANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA CLARA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA CRUZ DA CONCEICAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA CRUZ DA ESPERANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA CRUZ DAS PALMEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA CRUZ DO RIO PARDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA ERNESTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA FE DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA GERTRUDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA ISABEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA LUCIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA MARIA DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA MERCEDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTANA DA PONTE PENSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTANA DE PARNAIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA RITA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA RITA DO PASSA QUATRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA ROSA DE VITERBO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA SALETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANASTACIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANDRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANTONIO DA ALEGRIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANTONIO DE POSSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANTONIO DO ARACANGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANTONIO DO JARDIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANTONIO DO PINHAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO EXPEDITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTOPOLIS DO AGUAPEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO BENTO DO SAPUCAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO BERNARDO DO CAMPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO CAETANO DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO CARLOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO FRANCISCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOAO DA BOA VISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOAO DAS DUAS PONTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOAO DE IRACEMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOAO DO PAU D'ALHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOAQUIM DA BARRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOSE DA BELA VISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOSE DO BARREIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOSE DO RIO PARDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOSE DO RIO PRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOSE DOS CAMPOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO LOURENCO DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO LUIS DO PARAITINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO MANUEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO MIGUEL ARCANJO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO PAULO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO PEDRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO PEDRO DO TURVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO ROQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO SEBASTIAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO SEBASTIAO DA GRAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO SIMAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO VICENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SARAPUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SARUTAIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SEBASTIANOPOLIS DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SERRA AZUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SERRANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SERRA NEGRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SERTAOZINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SETE BARRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SEVERINIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SILVEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SOCORRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SOROCABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SUD MENNUCCI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SUMARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SUZANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SUZANAPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TABAPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TABATINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TABOAO DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TACIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAGUAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAIACU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAIUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAMBAU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TANABI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAPIRAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAPIRATIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAQUARAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAQUARITINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAQUARITUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAQUARIVAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TARABAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TARUMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TATUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAUBATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TEJUPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TEODORO SAMPAIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TERRA ROXA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TIETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TIMBURI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TORRE DE PEDRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TORRINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TRABIJU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TREMEMBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TRES FRONTEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TUIUTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TUPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TUPI PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TURIUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TURMALINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UBARANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UBATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UBIRAJARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UCHOA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UNIAO PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> URANIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> URU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> URUPES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VALENTIM GENTIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VALINHOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VALPARAISO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VARGEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VARGEM GRANDE DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VARGEM GRANDE PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VARZEA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VERA CRUZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VINHEDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VIRADOURO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VISTA ALEGRE DO ALTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VITORIA BRASIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VOTORANTIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VOTUPORANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ZACARIAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CHAVANTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESTIVA GERBI</t>
+    <t xml:space="preserve">ADAMANTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADOLFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUAS DA PRATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUAS DE LINDOIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUAS DE SANTA BARBARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUAS DE SAO PEDRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUDOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALAMBARI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALFREDO MARCONDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTAIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTO ALEGRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALUMINIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVARES FLORENCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVARES MACHADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVARO DE CARVALHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVINLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMERICANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMERICO BRASILIENSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMERICO DE CAMPOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPARO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANALANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRADINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANHEMBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANHUMAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APARECIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APARECIDA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APIAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARACARIGUAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARACATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARACOIABA DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAMINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARANDU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAPEI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARARAQUARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARARAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARCO-IRIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREALVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREIAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREIOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIRANHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTUR NOGUEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARUJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASPASIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATIBAIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AURIFLAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVANHANDAVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BADY BASSITT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALBINOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALSAMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANANAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARAO DE ANTONINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARBOSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARIRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRA BONITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRA DO CHAPEU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRA DO TURVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRETOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRINHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARUERI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BATATAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAURU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEBEDOURO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENTO DE ABREU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BERNARDINO DE CAMPOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BERTIOGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BILAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIRIGUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIRITIBA MIRIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOA ESPERANCA DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOCAINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOFETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOITUVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOM JESUS DOS PERDOES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOM SUCESSO DE ITARARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORACEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORBOREMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOREBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTUCATU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRAGANCA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRAUNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREJO ALEGRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRODOWSKI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BROTAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BURI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BURITAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BURITIZAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABRALIA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABREUVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACAPAVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACHOEIRA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACONDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAFELANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIABU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJAMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJATI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJOBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJURU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPINA DO MONTE ALEGRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPINAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPO LIMPO PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPOS DO JORDAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPOS NOVOS PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANANEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANDIDO MOTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANDIDO RODRIGUES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANITAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPAO BONITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPELA DO ALTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPIVARI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARAGUATATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARAPICUIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARDOSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASA BRANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASSIA DOS COQUEIROS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASTILHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATANDUVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATIGUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEDRAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERQUEIRA CESAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERQUILHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CESARIO LANGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARQUEADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEMENTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOMBIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCHAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCHAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDEIROPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COROADOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORONEL MACEDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORUMBATAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSMOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSMORAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COTIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRAVINHOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTAIS PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRUZALIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRUZEIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUBATAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUNHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCALVADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIADEMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRCE REIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIVINOLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOBRADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOIS CORREGOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOLCINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOURADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRACENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUARTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUMONT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHAPORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELDORADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIAS FAUSTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELISIARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMBAUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMBU DAS ARTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMBU-GUACU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMILIANOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGENHEIRO COELHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPIRITO SANTO DO PINHAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPIRITO SANTO DO TURVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTRELA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTRELA DO NORTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUCLIDES DA CUNHA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARTURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO PRESTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERRAZ DE VASCONCELOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLORA RICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOREAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLORIDA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLORINEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO MORATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCO DA ROCHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIEL MONTEIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GALIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GASTAO VIDIGAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAVIAO PEIXOTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENERAL SALGADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GETULINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLICERIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAICARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAIMBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAPIACU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAPIARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARACAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARACI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARANI D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARANTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARARAPES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARAREMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARATINGUETA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAREI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARUJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARULHOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUATAPARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUZOLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HERCULANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOLAMBRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HORTOLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IACANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IACRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IARAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBIRAREMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBITINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBIUNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IEPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGARACU DO TIETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGARAPAVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGARATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGUAPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILHABELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILHA COMPRIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILHA SOLTEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDAIATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIAPORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INUBIA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPAUSSU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPEUNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPIGUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPORANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRACEMAPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRAPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRAPURU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITABERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAJOBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAJU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITANHAEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPECERICA DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPETININGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPEVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPEVI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPIRAPUA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPORANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAQUAQUECETUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITARARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITARIRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITATIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITATINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITIRAPINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITIRAPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITOBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITUPEVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITUVERAVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JABORANDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JABOTICABAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACAREI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACUPIRANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAGUARIUNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAMBEIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JANDIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JARDINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JARINU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JERIQUARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOANOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO RAMALHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE BONIFACIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIO MESQUITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUMIRIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNDIAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNQUEIROPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUQUIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUQUITIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAGOINHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARANJAL PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAVINIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAVRINHAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LENCOIS PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINDOIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LORENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOURDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOUVEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCELIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS ANTONIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZIANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUPERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUTECIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACAUBAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACEDONIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIRINQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIRIPORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANDURI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARABA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARACAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARAPOAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIAPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARILIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARTINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MENDONCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERIDIANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MESOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIGUELOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINEIROS DO TIETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRACATU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRA ESTRELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRANDOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRANTE DO PARANAPANEMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRASSOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRASSOLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOCOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOGI DAS CRUZES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOGI GUACU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOGI MIRIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOMBUCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONCOES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONGAGUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE ALEGRE DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE ALTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE APRAZIVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE AZUL PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE CASTELO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTEIRO LOBATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE MOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORRO AGUDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORUNGABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOTUCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MURUTINGA DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NARANDIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATIVIDADE DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAZARE PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEVES PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NHANDEARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIPOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA ALIANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA CAMPINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA CANAA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA CASTILHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA EUROPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA GRANADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA GUATAPORANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA LUZITANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA ODESSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVO HORIZONTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUPORANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCAUCU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIMPIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONDA VERDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORIENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORINDIUVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSASCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSCAR BRESSANE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSVALDO CRUZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OURINHOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUROESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OURO VERDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACAEMBU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALESTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALMARES PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALMEIRA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALMITAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANORAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAGUACU PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAIBUNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAISO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARANAPANEMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARANAPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARDINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARIQUERA-ACU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARISI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATROCINIO PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULICEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULINIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULISTANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO DE FARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDERNEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRA BELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRANOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDREGULHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRINHAS PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO DE TOLEDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENAPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEREIRA BARRETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEREIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERUIBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIACATU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIEDADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PILAR DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINDAMONHANGABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINDORAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINHALZINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIQUEROBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIQUETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRACAIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRACICABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRAJU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRAJUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRANGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRAPORA DO BOM JESUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRAPOZINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRASSUNUNGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRATININGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PITANGUEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANALTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLATINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLONI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POMPEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONGAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONTALINDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONTES GESTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POPULINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORANGABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTO FELIZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTO FERREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POTIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POTIRENDABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRACINHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRADOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRAIA GRANDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRATANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESIDENTE ALVES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESIDENTE BERNARDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESIDENTE EPITACIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESIDENTE PRUDENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESIDENTE VENCESLAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROMISSAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUADRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUEIROZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUELUZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUINTANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RANCHARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REDENCAO DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGENTE FEIJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGISTRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESTINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO BONITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO BRANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO CORRENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO DOS INDIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO GRANDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO PIRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO PRETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIVERSUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIFAINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RINCAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIO CLARO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIO DAS PEDRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIO GRANDE DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIOLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBIACEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBINEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SABINO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAGRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALES OLIVEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALESOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALMOURAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALTINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALTO DE PIRAPORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALTO GRANDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDOVALINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA ADELIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA ALBERTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA BARBARA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA BRANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA CLARA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA CRUZ DA CONCEICAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA CRUZ DA ESPERANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA CRUZ DAS PALMEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA CRUZ DO RIO PARDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA ERNESTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA FE DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA GERTRUDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA ISABEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA LUCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA MARIA DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA MERCEDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTANA DA PONTE PENSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTANA DE PARNAIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA RITA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA RITA DO PASSA QUATRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA ROSA DE VITERBO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA SALETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANASTACIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANDRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANTONIO DA ALEGRIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANTONIO DE POSSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANTONIO DO ARACANGUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANTONIO DO JARDIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANTONIO DO PINHAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO EXPEDITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTOPOLIS DO AGUAPEI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO BENTO DO SAPUCAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO CAETANO DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO CARLOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO FRANCISCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOAO DA BOA VISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOAO DAS DUAS PONTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOAO DE IRACEMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOAO DO PAU D'ALHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOAQUIM DA BARRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOSE DA BELA VISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOSE DO BARREIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOSE DO RIO PARDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOSE DO RIO PRETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOSE DOS CAMPOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO LOURENCO DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO LUIS DO PARAITINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO MANUEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO MIGUEL ARCANJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO PAULO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO PEDRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO PEDRO DO TURVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO ROQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO SEBASTIAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO SEBASTIAO DA GRAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO SIMAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO VICENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARAPUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARUTAIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEBASTIANOPOLIS DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERRA AZUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERRANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERRA NEGRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERTAOZINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SETE BARRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEVERINIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOCORRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOROCABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUD MENNUCCI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUZANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUZANAPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABAPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABATINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABOAO DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TACIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAGUAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIACU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIUVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TANABI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAPIRAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAPIRATIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAQUARAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAQUARITINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAQUARITUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAQUARIVAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TARABAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TARUMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAUBATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEJUPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEODORO SAMPAIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERRA ROXA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMBURI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORRE DE PEDRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORRINHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRABIJU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TREMEMBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRES FRONTEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUIUTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUPI PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURIUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURMALINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBARANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBIRAJARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCHOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIAO PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URUPES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALENTIM GENTIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALINHOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALPARAISO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARGEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARGEM GRANDE DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARGEM GRANDE PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARZEA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERA CRUZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VINHEDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIRADOURO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VISTA ALEGRE DO ALTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITORIA BRASIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VOTORANTIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VOTUPORANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZACARIAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAVANTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTIVA GERBI</t>
   </si>
 </sst>
 </file>
@@ -2048,7 +2048,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2179,8 +2179,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.39"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2190,7 +2189,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
